--- a/docs/02_基本設計/01_機能・画面一覧/KF-BD-001_機能一覧.xlsx
+++ b/docs/02_基本設計/01_機能・画面一覧/KF-BD-001_機能一覧.xlsx
@@ -69,7 +69,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -91,11 +91,44 @@
         <color rgb="00808080"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="00808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00808080"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +148,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:F16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -492,6 +526,9 @@
     <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="1" t="inlineStr">
         <is>
@@ -500,6 +537,8 @@
       </c>
     </row>
     <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -511,7 +550,7 @@
           <t>勤怠フロー</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
@@ -524,7 +563,7 @@
           <t>KF-BD-001</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -534,10 +573,10 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n"/>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -550,7 +589,7 @@
           <t>2026/10/03</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="2" t="inlineStr">
@@ -563,8 +602,10 @@
           <t>Wang Sheng</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n"/>
-    </row>
+      <c r="D12" s="9" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -611,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -670,6 +711,29 @@
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/04</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>F-12 パスワード変更（SCR-007）、F-13 アカウントロックを追加（KF-RD-002 §4 認証）。F-01 にメールアドレス正規化・トークン有効 2 時間を追記</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -683,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -745,7 +809,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>メールアドレスとパスワードで認証し、ロール別に画面を制御する</t>
+          <t>メールアドレスとパスワードで認証し、ロール別に画面を制御する。入力のメールアドレスは前後の空白除去・小文字化して照合する</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -763,7 +827,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>トークン有効 2 時間。失敗時の文言は原因を区別しない（E-001）</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -1108,6 +1176,80 @@
       <c r="G12" s="8" t="inlineStr">
         <is>
           <t>メール通知は将来拡張</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>F-12</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>パスワード変更</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>ログイン中の本人が現在のパスワードを入力して新しいパスワードに変更する。初期パスワードの利用者は変更が済むまで他画面へ進めない（12文字以上・英字と数字を両方含む）</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>全員（本人）</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>SCR-007</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>API-023。サーバー側での強制は未実装（画面遷移での誘導のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>F-13</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>アカウントロック</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>ログイン失敗が 5 回続くとアカウントを 30 分ロックし、ロック中は正しいパスワードでも拒否する（E-017）</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>SCR-001</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>管理者による手動解除は未実装（30 分で自動解除）</t>
         </is>
       </c>
     </row>

--- a/docs/02_基本設計/01_機能・画面一覧/KF-BD-001_機能一覧.xlsx
+++ b/docs/02_基本設計/01_機能・画面一覧/KF-BD-001_機能一覧.xlsx
@@ -51,7 +51,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -128,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -149,6 +154,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -573,7 +581,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -652,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -734,6 +742,52 @@
         </is>
       </c>
       <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>実装（バックエンド・フロントエンド）と照合。F-11 の関連画面を SCR-108（通知一覧）に変更。F-02/F-03/F-04/F-05 の利用ロールを全員に修正。F-06（SCR-301 は SCR-201 と共用）・F-07（手動付与のみ）・F-08（所属は画面固定）・F-10（SCR-203 は上長のみ）・F-12（サーバー側強制は実装済み）・F-13 の概要・備考を実装に合わせて修正</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>休憩・日中離席の打刻（F-02）と休憩・離席修正申請（F-03・SCR-109）の追加に合わせて改訂。F-02 の勤務時間の計算ルール・未実装項目、F-03 の関連画面・承認時の反映、F-05 の承認段「処理なし」表示、F-06 の対象申請種別を追記。F-08 の部署を部署一覧API取得に変更し、管理者設定パスワードのポリシー（12〜72文字・英字と数字）を追記。F-12 の要変更時のメニュー無効表示と旧トークン無効を追記</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -797,111 +851,115 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>F-01</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>ログイン・ログアウト</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>メールアドレスとパスワードで認証し、ロール別に画面を制御する。入力のメールアドレスは前後の空白除去・小文字化して照合する</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>メールアドレスとパスワードで認証し、ロール別に画面を制御する。入力のメールアドレスは前後の空白除去・小文字化して照合する。ログアウトは画面側でトークンを破棄する</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>SCR-001</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>トークン有効 2 時間。失敗時の文言は原因を区別しない（E-001）</t>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>トークン有効 2 時間。失敗時の文言は原因を区別しない（E-001）。サーバー側のトークン失効（ログアウト無効化）は未実装</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>F-02</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>出退勤打刻</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>出勤・退勤を記録し、勤務時間・残業時間を自動計算する</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>従業員</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>出勤・退勤に加えて、休憩・日中離席の開始／終了を打刻する（同じボタンが開始と終了を兼ねる）。勤務時間（離席は全て控除。休憩は打刻した合計を控除し、打刻が無い日は法定休憩を自動控除）・残業時間を自動計算する。自分の月次勤怠（日別・休憩・離席の区間・月合計）を参照する</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>SCR-102, SCR-103</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>ボタン打刻</t>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>ボタン打刻。実装は /home の 1 画面（打刻＋月次勤怠）。同時に開始中にできる休憩・離席は1つで、開始中は退勤できない（E-022）。時刻はサーバーが秒単位で記録する。休憩・離席の取消・削除、0分区間の自動破棄、休憩不足（法定未満）の警告は【未実装（今後対応）】</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>F-03</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>打刻修正申請</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>打刻漏れ・誤りの修正を理由付きで申請し、承認後に反映する</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>従業員</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>SCR-104</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>打刻漏れ・誤りの修正（打刻修正申請：対象日の出勤・退勤時刻）と、休憩・離席の修正（休憩・離席修正申請：対象日・種別・開始・終了）を理由付きで申請し、承認後に打刻へ反映する。下書き保存・再提出が可能</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>SCR-104, SCR-109</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>実装は申請フォーム（/requests/new）で申請種別（休暇申請／打刻修正申請／休憩・離席修正申請）を切り替える（SCR-105・SCR-109 と共用）。承認は上長→管理者の2段階。最終承認で打刻へ反映（打刻修正は休憩・離席を考慮して勤務・残業を再計算、休憩・離席修正は同種別の継続中区間の修正または区間の追加）。休憩・離席修正は提出時と承認時に再検証する（E-003／E-005）。申請期限（翌月 3 営業日）は【未実装（今後対応）】</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -916,12 +974,12 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>休暇種別・期間・理由を入力して申請。残日数を自動チェックする</t>
+          <t>休暇種別・期間・理由を入力して申請。日数は土日・祝日を除く営業日で計算し、残日数を提出時にチェックする（承認待ち分を引当）。半休可（種別による）。下書き保存が可能</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>従業員</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -934,7 +992,7 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -949,12 +1007,12 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>承認前の申請を取り下げる</t>
+          <t>自分の申請の一覧・詳細（承認履歴）を参照し、承認前（下書き・承認待ち・差戻し）の申請を取り下げる。下書き・差戻しの申請を提出（再提出）する</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>従業員</t>
+          <t>全員</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -967,7 +1025,11 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>差戻し後の内容修正画面は無い（そのまま再提出するか、取り下げて新規申請）。取下げ・差戻し・却下で打ち切られた申請の未処理の承認段は「処理なし」と表示する</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -982,7 +1044,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>承認待ち一覧から多段フローで処理する。差戻し・却下時はコメント必須</t>
+          <t>承認待ち一覧から多段フローで処理する（対象は休暇申請・打刻修正申請・休憩・離席修正申請）。差戻し・却下時はコメント必須。自分の申請は処理できない。最終承認で、休暇は残日数の消化、打刻修正・休憩・離席修正は打刻への反映を行う</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1002,79 +1064,83 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>上長→管理者の2段</t>
+          <t>上長→管理者の2段（申請者に有効な上長がいない場合は管理者のみ）。SCR-301 は SCR-201 と同一画面（承認段階 2 段目で絞込）。承認・差戻し・却下は申請詳細（SCR-202）からも実行できる</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>F-07</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>休暇残日数管理</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>年次有給休暇の付与・消化・残日数を管理する</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>年次有給休暇ほか休暇種別の付与・消化・残日数を管理する（付与行ごとの失効日＝付与日の 2 年後、消化は失効日の早い順）。管理者が付与・調整する</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>全員（設定は管理者）</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>SCR-107, SCR-305</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>年5日取得義務の進捗を表示</t>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>年5日取得義務の進捗・次回付与予定日を表示。付与は手動のみ（自動付与バッチ BAT-001・年5日アラート BAT-002 は未実装）</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>F-08</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>ユーザー管理</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>ユーザー・ロール・所属・承認ルートの登録・変更</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>ユーザー・ロール・所属・上長（承認ルートの 1 段目）の登録・変更・無効化、パスワード再設定（初期パスワード・再設定パスワードは12〜72文字・半角英数字記号のみ・英字と数字を両方含む）</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>管理者</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>SCR-302</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>物理削除なし。パスワード再設定でロックも解除され、対象ユーザーは次回ログイン後にパスワード変更が必要になる（以前のトークンは無効）。所属（部署）の選択肢は GET /api/departments から取得する（画面固定ではない）。部署のマスタ保守画面・登録APIは【未実装（今後対応）】</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1089,7 +1155,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>休暇種別・付与ルール・祝日カレンダーの設定</t>
+          <t>休暇種別（有給区分・日数ルール・半日可・有効）と祝日・会社休日カレンダーの設定</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1107,75 +1173,83 @@
           <t>MVP</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>年次有給休暇の主要項目は変更不可。付与ルールのマスタは無い（付与は F-07）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>F-10</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>集計・一覧</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>月次の勤怠・休暇の集計と一覧。CSV出力</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>月次の勤怠・休暇の集計。管理者は全社・部署別の集計と CSV 出力（RPT-001）、上長は直属の部下の集計（画面表示のみ）</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>上長・管理者</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>SCR-203, SCR-306</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr"/>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>SCR-203 は上長のみ（管理者は不可）。個別の勤怠一覧画面は無く、集計のみ。月間残業 45 時間超は赤字表示（アラート通知は未実装）。管理者の集計画面の部署プルダウンは GET /api/departments から取得</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>F-11</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>申請・承認・却下時の画面内通知</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>申請提出・承認・差戻し・却下・取下げ・休暇付与の画面内通知。一覧（最新 50 件）・既読化・ヘッダーのベル（未読件数）</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>SCR-101</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>SCR-108</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>メール通知は将来拡張</t>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>メール通知は将来拡張（未実装）。年5日アラート（LEAVE_ALERT）は発行元バッチが未実装。ホームへの通知要約は未実装</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1266,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>ログイン中の本人が現在のパスワードを入力して新しいパスワードに変更する。初期パスワードの利用者は変更が済むまで他画面へ進めない（12文字以上・英字と数字を両方含む）</t>
+          <t>ログイン中の本人が現在のパスワードを入力して新しいパスワードに変更する。初期パスワード・管理者再設定直後の利用者は変更が済むまで他の機能を使えない（12文字以上・英字と数字を両方含む）。管理者が設定する初期パスワード・再設定パスワード（SCR-302）にも同じポリシーを適用する</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1212,44 +1286,44 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>API-023。サーバー側での強制は未実装（画面遷移での誘導のみ）</t>
+          <t>API-023。サーバー側で強制（E-019）。変更成功後は再ログインが必要（変更前に発行されたトークンは無効）。要変更の間は画面の左メニューを無効表示にして案内文を出す</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>F-13</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>アカウントロック</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>ログイン失敗が 5 回続くとアカウントを 30 分ロックし、ロック中は正しいパスワードでも拒否する（E-017）</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>SCR-001</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>管理者による手動解除は未実装（30 分で自動解除）</t>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>専用の手動解除は未実装（30 分で自動解除。管理者のパスワード再設定でも解除される）</t>
         </is>
       </c>
     </row>
